--- a/password_manager/密码记录导入模板.xlsx
+++ b/password_manager/密码记录导入模板.xlsx
@@ -1,138 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwb\Desktop\pwd_glgj\password_manager\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2C48FC-9BA0-4A18-A021-9F6425708EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="密码记录模板" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="密码记录模板" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>项目名称 *</t>
-  </si>
-  <si>
-    <t>功能</t>
-  </si>
-  <si>
-    <t>IP地址 *</t>
-  </si>
-  <si>
-    <t>账户 *</t>
-  </si>
-  <si>
-    <t>密码 *</t>
-  </si>
-  <si>
-    <t>所在区域</t>
-  </si>
-  <si>
-    <t>网络类型</t>
-  </si>
-  <si>
-    <t>其他账号</t>
-  </si>
-  <si>
-    <t>示例-OA系统</t>
-  </si>
-  <si>
-    <t>系统管理</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>P@ssw0rd</t>
-  </si>
-  <si>
-    <t>北京总部</t>
-  </si>
-  <si>
-    <t>内网</t>
-  </si>
-  <si>
-    <t>备用账号: auditor</t>
-  </si>
-  <si>
-    <t>192.168.8.90</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <i val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6F0F9"/>
-        <bgColor rgb="FFE6F0F9"/>
+        <fgColor rgb="00E6F0F9"/>
+        <bgColor rgb="00E6F0F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD9D9"/>
-        <bgColor rgb="FFFFD9D9"/>
+        <fgColor rgb="00FFD9D9"/>
+        <bgColor rgb="00FFD9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,32 +68,89 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,117 +438,142 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="25" customWidth="1"/>
-    <col min="6" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>项目名称 *</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>IP地址 *</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>账户 *</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>密码 *</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>所在区域</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>网络类型</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>其他账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>示例-OA系统</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>系统管理</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>192.168.1.100</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>P@ssw0rd</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>北京总部</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>备用账号: auditor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>使用说明:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. 标记 * 的列为必填项 (项目名称、IP地址、账户、密码)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. 请按照示例行的格式填写数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3. 填写完成后删除示例行</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4. 保存文件后使用"导入"功能导入数据</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -581,7 +583,6 @@
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>